--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/biobio.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1246,7 +1246,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1057420-102-CM26</t>
+          <t>4650-272-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>SECAPPS TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>77.660.154-3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8341.08</v>
+        <v>35909.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3734-150-CM26</t>
+          <t>1057420-102-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.170.300-2</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAJA</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>9403.809999999999</v>
+        <v>8341.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4079-68-CM26</t>
+          <t>3734-150-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.151.000-k</t>
+          <t>69.170.300-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>I MUNICIPALIDAD DE LAJA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>76.376.088-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>16687.89</v>
+        <v>9403.809999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2078-723-CM26</t>
+          <t>4079-68-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.151.000-k</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.083.021-6</t>
+          <t>76.260.080-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>55872.01</v>
+        <v>16687.89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1057415-2855-CM26</t>
+          <t>2078-723-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ANTICA S.A.</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.707.140-k</t>
+          <t>76.083.021-6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8612.389999999999</v>
+        <v>55872.01</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1057414-238-CM26</t>
+          <t>1057415-2855-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>ANTICA S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.707.140-k</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>750328.3100000001</v>
+        <v>8612.389999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1305504-68-CM26</t>
+          <t>1057414-238-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DISEÑO Y DESARROLLO VISUALMENTE SPA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.046.871-1</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>19620.53</v>
+        <v>750328.3100000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2664-398-CM26</t>
+          <t>1305504-68-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.150.102-7</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>Diseño y Desarrollo Visualmente SpA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.046.871-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7267.5</v>
+        <v>19620.53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1057415-2966-CM26</t>
+          <t>2664-398-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>69.150.102-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>14346.73</v>
+        <v>7267.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1057421-461-CM26</t>
+          <t>1057415-2966-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.607.306-0</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE LAJA</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>17412.68</v>
+        <v>14346.73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057421-460-CM26</t>
+          <t>1057421-461-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>20314.86</v>
+        <v>17412.68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2410-423-CM26</t>
+          <t>1057421-460-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>61.607.306-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE LAJA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ASIMOV CONSULTORES SPA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,6 +1972,67 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
+        <v>20314.86</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2410-423-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.170.102-6</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASIMOV CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76.372.725-4</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
         <v>9704.5</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/biobio.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -684,7 +684,11 @@
           <t>77.063.770-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>76.376.088-k</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.063.770-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1124,7 +1136,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1057417-41801-CM25</t>
+          <t>1057414-768-SE25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1151,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1161,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,28 +1176,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7392.11</v>
+        <v>77508.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2760-96-CM25</t>
+          <t>1057417-41801-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1211,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1241,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SECAPPS TECHNOLOGIES SPA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.660.154-3</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1256,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8044.33</v>
+        <v>7392.11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4650-272-CM25</t>
+          <t>2760-96-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1277,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1287,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1294,20 +1310,24 @@
           <t>77.660.154-3</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>35909.28</v>
+        <v>8044.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1057420-102-CM26</t>
+          <t>4650-272-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1337,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,28 +1367,32 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>SECAPPS TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>77.660.154-3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8341.08</v>
+        <v>35909.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3734-150-CM26</t>
+          <t>1057420-102-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,22 +1407,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.170.300-2</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAJA</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1432,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1447,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>9403.809999999999</v>
+        <v>8341.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4079-68-CM26</t>
+          <t>3734-150-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,22 +1468,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.151.000-k</t>
+          <t>69.170.300-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>I MUNICIPALIDAD DE LAJA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,28 +1493,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>16687.89</v>
+        <v>9403.809999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2078-723-CM26</t>
+          <t>4079-68-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1528,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1543,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.151.000-k</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,28 +1558,32 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.083.021-6</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>55872.01</v>
+        <v>16687.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1057415-2855-CM26</t>
+          <t>2078-723-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1598,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1608,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1623,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ANTICA S.A.</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.707.140-k</t>
+          <t>76.083.021-6</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1638,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>8612.389999999999</v>
+        <v>55872.01</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1057414-238-CM26</t>
+          <t>1057415-2855-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1654,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1669,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1684,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>ANTICA S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.707.140-k</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1699,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>750328.3100000001</v>
+        <v>8612.389999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1305504-68-CM26</t>
+          <t>1057414-238-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,22 +1720,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,28 +1745,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Diseño y Desarrollo Visualmente SpA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.046.871-1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>19620.53</v>
+        <v>750328.3100000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2664-398-CM26</t>
+          <t>1305504-68-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1780,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1795,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.150.102-7</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOME</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1810,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>Diseño y Desarrollo Visualmente SpA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.046.871-1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1825,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7267.5</v>
+        <v>19620.53</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1057415-2966-CM26</t>
+          <t>2664-398-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1841,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1856,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>69.150.102-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,28 +1871,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>14346.73</v>
+        <v>7267.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057421-461-CM26</t>
+          <t>1057415-2966-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1906,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.607.306-0</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE LAJA</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,7 +1951,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>17412.68</v>
+        <v>14346.73</v>
       </c>
     </row>
     <row r="25">
@@ -1978,7 +2018,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2410-423-CM26</t>
+          <t>1057421-461-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +2028,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>61.607.306-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE LAJA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2058,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASIMOV CONSULTORES SPA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,6 +2073,132 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
+        <v>17412.68</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1057414-512-SE26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.607.300-1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD BIO BIO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PRAGMA INFORMATICA S.A.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>2956.49</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2410-423-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.170.102-6</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ASIMOV CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.372.725-4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
         <v>9704.5</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/biobio.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2202,6 +2202,71 @@
         <v>9704.5</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1057414-652-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>61.607.300-1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD BIO BIO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>PRAGMA INFORMATICA S.A.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>66920.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/biobio.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/biobio.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/biobio.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1957,7 +1957,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057421-460-CM26</t>
+          <t>1057421-461-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2012,13 +2012,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>20314.86</v>
+        <v>17412.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057421-461-CM26</t>
+          <t>1057421-460-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>17412.68</v>
+        <v>20314.86</v>
       </c>
     </row>
     <row r="27">
@@ -2265,6 +2265,67 @@
       </c>
       <c r="M29" s="2" t="n">
         <v>66920.25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2785-755-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.264.800-5</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>TCHILECOM</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>77.349.120-8</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>18303.93</v>
       </c>
     </row>
   </sheetData>
